--- a/business_forms/032_store_rota_management_form--business_forms.xlsx
+++ b/business_forms/032_store_rota_management_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -945,8 +945,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -974,12 +974,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_21,_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 21, 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_22,_'value':_'assistant_manager'}</t>
+          <t>assistant_manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 22, 'value': 'Assistant Manager'}</t>
+          <t>Assistant Manager</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_23,_'value':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 23, 'value': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_24,_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 24, 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_26,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 26, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_27,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 27, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
